--- a/team.xlsx
+++ b/team.xlsx
@@ -578,6 +578,9 @@
       <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="C5" s="1" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">

--- a/team.xlsx
+++ b/team.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t xml:space="preserve">01040739210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ريتاج احمد عبدالرحمن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01211097254</t>
   </si>
 </sst>
 </file>
@@ -619,6 +625,9 @@
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="C9" s="1" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
@@ -800,6 +809,9 @@
       <c r="B29" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="C29" s="1" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
@@ -808,10 +820,17 @@
       <c r="B30" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="C30" s="1" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3"/>
-      <c r="B31" s="4"/>
+      <c r="A31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/team.xlsx
+++ b/team.xlsx
@@ -734,6 +734,9 @@
       <c r="B20" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="C20" s="1" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
@@ -753,6 +756,9 @@
       <c r="B22" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="C22" s="1" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
@@ -761,6 +767,9 @@
       <c r="B23" s="4" t="s">
         <v>46</v>
       </c>
+      <c r="C23" s="1" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
@@ -793,6 +802,9 @@
       <c r="B27" s="4" t="s">
         <v>54</v>
       </c>
+      <c r="C27" s="1" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
@@ -830,6 +842,9 @@
       </c>
       <c r="B31" s="4" t="s">
         <v>62</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
